--- a/public/exports/29189463.xlsx
+++ b/public/exports/29189463.xlsx
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3336927</t>
+          <t xml:space="preserve">404028, 404029</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F3">
-        <v>254</v>
+        <v>2498</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,7 +181,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">751199, 3332171</t>
+          <t xml:space="preserve">751233, 3292853</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>460</v>
+        <v>2571</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,7 +231,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">751233, 3292853</t>
+          <t xml:space="preserve">9577061</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -240,21 +240,21 @@
         </is>
       </c>
       <c r="F5">
-        <v>2571</v>
+        <v>296</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014710</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -281,7 +281,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9577061</t>
+          <t xml:space="preserve">3303892</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -290,16 +290,16 @@
         </is>
       </c>
       <c r="F6">
-        <v>296</v>
+        <v>2359</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014710</t>
+          <t xml:space="preserve">200033540</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2020-07-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -331,7 +331,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3303892</t>
+          <t xml:space="preserve">3336883</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -340,16 +340,16 @@
         </is>
       </c>
       <c r="F7">
-        <v>2359</v>
+        <v>4220</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033540</t>
+          <t xml:space="preserve">200041825</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-05</t>
+          <t xml:space="preserve">2020-11-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3336883</t>
+          <t xml:space="preserve">751199, 3332171</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,16 +390,16 @@
         </is>
       </c>
       <c r="F8">
-        <v>4220</v>
+        <v>460</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041825</t>
+          <t xml:space="preserve">311138078</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-26</t>
+          <t xml:space="preserve">2025-10-02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632692</t>
+          <t xml:space="preserve">311632691</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1236,15 +1236,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F25">
-        <v>1186</v>
+        <v>254</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651821</t>
+          <t xml:space="preserve">311651823</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1286,15 +1286,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F26">
-        <v>736</v>
+        <v>1186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651822</t>
+          <t xml:space="preserve">311651821</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1336,15 +1336,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F27">
-        <v>457</v>
+        <v>736</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651821</t>
+          <t xml:space="preserve">311651822</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1381,20 +1381,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378205</t>
+          <t xml:space="preserve">3336927</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F28">
-        <v>486</v>
+        <v>457</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651820</t>
+          <t xml:space="preserve">311651821</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1431,20 +1431,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002043</t>
+          <t xml:space="preserve">3378205</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F29">
-        <v>784</v>
+        <v>486</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651796</t>
+          <t xml:space="preserve">311651820</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378205</t>
+          <t xml:space="preserve">7002043</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="F30">
-        <v>622</v>
+        <v>784</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664900</t>
+          <t xml:space="preserve">311651796</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-08</t>
+          <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>800</v>
+        <v>622</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1586,11 +1586,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F32">
-        <v>696</v>
+        <v>800</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1636,11 +1636,11 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F33">
-        <v>1345</v>
+        <v>696</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F34">
-        <v>3110</v>
+        <v>1345</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F35">
-        <v>1127</v>
+        <v>3110</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,25 +1781,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333756</t>
+          <t xml:space="preserve">3378205</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F36">
-        <v>2003</v>
+        <v>1127</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666554</t>
+          <t xml:space="preserve">311664900</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-15</t>
+          <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3334183</t>
+          <t xml:space="preserve">3333756</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,16 +1840,16 @@
         </is>
       </c>
       <c r="F37">
-        <v>588</v>
+        <v>2003</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670124</t>
+          <t xml:space="preserve">311666554</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3334184</t>
+          <t xml:space="preserve">3334183</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,11 +1890,11 @@
         </is>
       </c>
       <c r="F38">
-        <v>417</v>
+        <v>588</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670125</t>
+          <t xml:space="preserve">311670124</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3336437</t>
+          <t xml:space="preserve">3334184</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1940,11 +1940,11 @@
         </is>
       </c>
       <c r="F39">
-        <v>5971</v>
+        <v>417</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670120</t>
+          <t xml:space="preserve">311670125</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1986,15 +1986,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>510</v>
+        <v>5971</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670123</t>
+          <t xml:space="preserve">311670120</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2036,15 +2036,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F41">
-        <v>286</v>
+        <v>510</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670120</t>
+          <t xml:space="preserve">311670123</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2086,11 +2086,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F42">
-        <v>1935</v>
+        <v>286</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2136,15 +2136,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F43">
-        <v>505</v>
+        <v>1935</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670123</t>
+          <t xml:space="preserve">311670120</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2181,20 +2181,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7823049</t>
+          <t xml:space="preserve">3336437</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F44">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670128</t>
+          <t xml:space="preserve">311670123</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292910</t>
+          <t xml:space="preserve">7823049</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="F45">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671358</t>
+          <t xml:space="preserve">311670128</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-03</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3293217</t>
+          <t xml:space="preserve">3292910</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,11 +2290,11 @@
         </is>
       </c>
       <c r="F46">
-        <v>552</v>
+        <v>465</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671360</t>
+          <t xml:space="preserve">311671358</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3303660</t>
+          <t xml:space="preserve">3293217</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,11 +2340,11 @@
         </is>
       </c>
       <c r="F47">
-        <v>255</v>
+        <v>552</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671359</t>
+          <t xml:space="preserve">311671360</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2381,20 +2381,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255541</t>
+          <t xml:space="preserve">3303660</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>683</v>
+        <v>255</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671364</t>
+          <t xml:space="preserve">311671359</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2431,20 +2431,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8149234</t>
+          <t xml:space="preserve">7255541</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F49">
-        <v>3462</v>
+        <v>683</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671363</t>
+          <t xml:space="preserve">311671364</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3294980</t>
+          <t xml:space="preserve">8149234</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="F50">
-        <v>513</v>
+        <v>3462</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682078</t>
+          <t xml:space="preserve">311671363</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-22</t>
+          <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,20 +2531,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255541</t>
+          <t xml:space="preserve">3294980</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>1141</v>
+        <v>513</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682093</t>
+          <t xml:space="preserve">311682078</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2586,15 +2586,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F52">
-        <v>3384</v>
+        <v>1141</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682070</t>
+          <t xml:space="preserve">311682093</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2631,20 +2631,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9851910</t>
+          <t xml:space="preserve">7255541</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F53">
-        <v>1095</v>
+        <v>3384</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682069</t>
+          <t xml:space="preserve">311682070</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3331963</t>
+          <t xml:space="preserve">9851910</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="F54">
-        <v>3851</v>
+        <v>1095</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685452</t>
+          <t xml:space="preserve">311682069</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-05</t>
+          <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333698</t>
+          <t xml:space="preserve">3331963</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,11 +2740,11 @@
         </is>
       </c>
       <c r="F55">
-        <v>967</v>
+        <v>3851</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685453</t>
+          <t xml:space="preserve">311685452</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2781,20 +2781,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255541</t>
+          <t xml:space="preserve">3333698</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>501</v>
+        <v>967</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685449</t>
+          <t xml:space="preserve">311685453</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2831,20 +2831,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7566589</t>
+          <t xml:space="preserve">7255541</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F57">
-        <v>774</v>
+        <v>501</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685454</t>
+          <t xml:space="preserve">311685449</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2881,20 +2881,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8149234</t>
+          <t xml:space="preserve">7566589</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F58">
-        <v>1028</v>
+        <v>774</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685451</t>
+          <t xml:space="preserve">311685454</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378471</t>
+          <t xml:space="preserve">8149234</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F59">
-        <v>873</v>
+        <v>1028</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685795</t>
+          <t xml:space="preserve">311685451</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-06</t>
+          <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292911</t>
+          <t xml:space="preserve">3378471</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F60">
-        <v>755</v>
+        <v>873</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691495</t>
+          <t xml:space="preserve">311685795</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-29</t>
+          <t xml:space="preserve">2033-06-06</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3294080</t>
+          <t xml:space="preserve">3292911</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="F61">
-        <v>635</v>
+        <v>755</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691496</t>
+          <t xml:space="preserve">311691495</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">100017011</t>
+          <t xml:space="preserve">3294080</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="F62">
-        <v>1111</v>
+        <v>635</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692201</t>
+          <t xml:space="preserve">311691496</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-03</t>
+          <t xml:space="preserve">2033-06-29</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054028</t>
+          <t xml:space="preserve">100017011</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,11 +3140,11 @@
         </is>
       </c>
       <c r="F63">
-        <v>361</v>
+        <v>1111</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692197</t>
+          <t xml:space="preserve">311692201</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802041</t>
+          <t xml:space="preserve">100054028</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,11 +3190,11 @@
         </is>
       </c>
       <c r="F64">
-        <v>754</v>
+        <v>361</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692200</t>
+          <t xml:space="preserve">311692197</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292865</t>
+          <t xml:space="preserve">1802041</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,11 +3240,11 @@
         </is>
       </c>
       <c r="F65">
-        <v>4266</v>
+        <v>754</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692220</t>
+          <t xml:space="preserve">311692200</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3293205</t>
+          <t xml:space="preserve">3292865</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,11 +3290,11 @@
         </is>
       </c>
       <c r="F66">
-        <v>9432</v>
+        <v>4266</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692210</t>
+          <t xml:space="preserve">311692220</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378118</t>
+          <t xml:space="preserve">3293205</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,11 +3340,11 @@
         </is>
       </c>
       <c r="F67">
-        <v>1134</v>
+        <v>9432</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692224</t>
+          <t xml:space="preserve">311692210</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378421</t>
+          <t xml:space="preserve">3378118</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,11 +3390,11 @@
         </is>
       </c>
       <c r="F68">
-        <v>262</v>
+        <v>1134</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692205</t>
+          <t xml:space="preserve">311692224</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3431,20 +3431,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255541</t>
+          <t xml:space="preserve">3378421</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F69">
-        <v>371</v>
+        <v>262</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692204</t>
+          <t xml:space="preserve">311692205</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3481,20 +3481,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8021033</t>
+          <t xml:space="preserve">7255541</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F70">
-        <v>673</v>
+        <v>371</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692209</t>
+          <t xml:space="preserve">311692204</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3531,20 +3531,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425182</t>
+          <t xml:space="preserve">8021033</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>417</v>
+        <v>673</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692199</t>
+          <t xml:space="preserve">311692209</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3581,20 +3581,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9545107</t>
+          <t xml:space="preserve">9425182</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F72">
-        <v>1225</v>
+        <v>417</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692203</t>
+          <t xml:space="preserve">311692199</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3631,20 +3631,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9545112</t>
+          <t xml:space="preserve">9545107</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F73">
-        <v>889</v>
+        <v>1225</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692202</t>
+          <t xml:space="preserve">311692203</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3681,20 +3681,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9577061</t>
+          <t xml:space="preserve">9545112</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F74">
-        <v>1230</v>
+        <v>889</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692206</t>
+          <t xml:space="preserve">311692202</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024720</t>
+          <t xml:space="preserve">9577061</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F75">
-        <v>607</v>
+        <v>1230</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697532</t>
+          <t xml:space="preserve">311692206</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-01</t>
+          <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339194</t>
+          <t xml:space="preserve">100024720</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,11 +3790,11 @@
         </is>
       </c>
       <c r="F76">
-        <v>783</v>
+        <v>607</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697529</t>
+          <t xml:space="preserve">311697532</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425182</t>
+          <t xml:space="preserve">3339194</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,11 +3840,11 @@
         </is>
       </c>
       <c r="F77">
-        <v>3530</v>
+        <v>783</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697527</t>
+          <t xml:space="preserve">311697529</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">404028, 404029</t>
+          <t xml:space="preserve">9425182</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>2498</v>
+        <v>3530</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703362</t>
+          <t xml:space="preserve">311697527</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-29</t>
+          <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">

--- a/public/exports/29189463.xlsx
+++ b/public/exports/29189463.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:L83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stendalsvej 7</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10194118</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>253</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skørpingvej 5A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9575</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">404028, 404029</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>2498</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestre Primærvej 7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">751233, 3292853</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>2571</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nøragervej 9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">9577061</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>296</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">200014710</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Birkehøjvej 10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">3303892</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>2359</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">200033540</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-07-05</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Buderupholmvej 57</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336883</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>4220</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">200041825</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-11-26</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østre Skovvej 16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9574</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">751199, 3332171</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>460</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">311138078</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-02</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jyllandsgade 30</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336242</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>254</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">311244393</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">9402109</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>2771</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">311603283</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-25</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terndrup Halvej 1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9575</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">9614946</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>5724</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">311632690</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-10-03</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovvej 4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9575</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">9614946</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>349</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311632691</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311632692</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-10-03</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hjedsbækvej 289</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9541</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">7002043</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>1907</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">311642734</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hjedsbækvej 289</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9541</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">7002043</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>4027</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311642734</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hjedsbækvej 289</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9541</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">7002043</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>300</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311642734</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hjedsbækvej 289</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9541</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">7002043</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>400</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311642734</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skibstedvej 26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9293</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">3335469</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>990</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311651018</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skibstedvej 26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9293</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">3335469</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>516</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311651018</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mastrupvej 75</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">3292864</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>7550</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311651797</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mastrupvej 75A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">3292864</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>420</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311651798</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mastrupvej 75B</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">3292864</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>903</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311651799</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Birkehøjvej 8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">3303955</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>3940</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311651818</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rebild Skovhusevej 2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">3335702</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1421</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311651794</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sverriggårdsvej 4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336927</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>970</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311651821</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311651823</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sverriggårdsvej 4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336927</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>254</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311651823</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sverriggårdsvej 4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336927</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1186</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311651821</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311651823</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sverriggårdsvej 4A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336927</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>736</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311651822</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sverriggårdsvej 2A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336927</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>457</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311651821</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311651823</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løgstørvej 165</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378205</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>486</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311651820</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hjedsbækvej 287</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9541</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">7002043</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>784</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311651796</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løgstørvej 161</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378205</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>622</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311664900</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løgstørvej 161</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378205</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>800</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311664900</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løgstørvej 161</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378205</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>696</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311664900</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løgstørvej 161</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378205</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>1345</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311664900</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løgstørvej 161</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378205</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>3110</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311664900</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løgstørvej 161</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378205</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1127</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311664900</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skørpingvej 7</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9575</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">3333756</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>2003</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311666554</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terndrup Center 3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9575</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">3334183</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>588</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311670124</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terndrup Center 6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9575</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">3334184</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>417</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311670125</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Himmerlandsvej 65</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336437</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>5971</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311670120</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Himmerlandsvej 63</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336437</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>510</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311670123</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Himmerlandsvej 67</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336437</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>286</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311670120</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Himmerlandsvej 65</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336437</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>1935</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311670120</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Himmerlandsvej 61</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">3336437</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>505</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311670123</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Degnevænget 25</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">7823049</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>467</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311670128</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brunagervej 2A</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">3292910</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>465</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311671358</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnebakken 99</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">3293217</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>552</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311671360</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gammel Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">3303660</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>255</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311671359</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grangårdsvej 13A</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">7255541</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>683</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311671364</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Himmerlandshave 1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9541</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">8149234</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>3462</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311671363</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mastrupvej 63</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">3294980</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>513</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311682078</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grangårdsvej 11</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">7255541</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>1141</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311682093</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hobrovej 110</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">7255541</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>3384</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311682070</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kr. Østergårdsvej 2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">9851910</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>1095</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311682069</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevangen 1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9574</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">3331963</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>3851</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311685452</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aavangen 2C</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9575</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">3333698</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>967</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311685453</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hobrovej 108</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">7255541</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>501</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311685449</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hermesvej 47</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">7566589</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>774</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311685454</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Himmerlandshave 2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9541</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">8149234</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>1028</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311685451</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sortebakken 7</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378471</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>873</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311685795</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-06</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mastrupvej 90</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">3292911</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>755</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311691495</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-29</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rafns Alle 3</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">3294080</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>635</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311691496</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-06-29</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kronhjorten 2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">100017011</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>1111</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311692201</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rebildvej 25A</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">100054028</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>361</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311692197</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Haverslevvej 156</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">1802041</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>754</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311692200</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mastruplundvej 2L</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">3292865</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>4266</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311692220</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnebakken 105</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">3293205</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>9432</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311692210</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestermarksvej 2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378118</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>1134</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311692224</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jernbanegade 18A</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">3378421</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>262</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311692205</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grangårdsvej 13C</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">7255541</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>371</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311692204</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nibevej 164A</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">8021033</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>673</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311692209</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grønnegade 1A</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9574</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">9425182</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>417</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311692199</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klepholmvej 5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">9545107</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>1225</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311692203</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådyret 2</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">9545112</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>889</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311692202</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jernbanegade 9</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9610</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">9577061</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>1230</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311692206</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gammel Skørpingvej 100</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">100024720</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>607</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311697532</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skørpingvej 78</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9520</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">3339194</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>783</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311697529</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 2</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9574</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">9425182</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>3530</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311697527</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brunagervej 1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">751231, 9993929</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>3621</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311744559</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terndrup Halvej 3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9575</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">751202, 9614946</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>3007</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311756087</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-01</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnebakken 103</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">751225, 3293216</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>2150</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311756082</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-01</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hjedsbækvej 291</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9541</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">751227, 3306436</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>2244</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311756076</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-01</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,39 +4951,49 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bundgaardsmindevej 34</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9530</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">100634939</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>1646</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311838458</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J83"/>
+  <autoFilter ref="A1:L83"/>
 </worksheet>
 </file>
--- a/public/exports/29189463.xlsx
+++ b/public/exports/29189463.xlsx
@@ -151,17 +151,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skørpingvej 5A</t>
+          <t xml:space="preserve">Vestre Primærvej 7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9575</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404028, 404029</t>
+          <t xml:space="preserve">751233, 3292853</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>2498</v>
+        <v>2571</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,17 +211,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Primærvej 7</t>
+          <t xml:space="preserve">Nøragervej 9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9610</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">751233, 3292853</t>
+          <t xml:space="preserve">9577061</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,21 +230,21 @@
         </is>
       </c>
       <c r="H4">
-        <v>2571</v>
+        <v>296</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014710</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -271,17 +271,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøragervej 9</t>
+          <t xml:space="preserve">Birkehøjvej 10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9610</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9577061</t>
+          <t xml:space="preserve">3303892</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -290,16 +290,16 @@
         </is>
       </c>
       <c r="H5">
-        <v>296</v>
+        <v>2359</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014710</t>
+          <t xml:space="preserve">200033540</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-09</t>
+          <t xml:space="preserve">2020-07-05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -331,17 +331,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkehøjvej 10</t>
+          <t xml:space="preserve">Buderupholmvej 57</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9520</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3303892</t>
+          <t xml:space="preserve">3336883</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -350,16 +350,16 @@
         </is>
       </c>
       <c r="H6">
-        <v>2359</v>
+        <v>4220</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033540</t>
+          <t xml:space="preserve">200041825</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-05</t>
+          <t xml:space="preserve">2020-11-26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -391,17 +391,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buderupholmvej 57</t>
+          <t xml:space="preserve">Østre Skovvej 16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520</t>
+          <t xml:space="preserve">9574</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3336883</t>
+          <t xml:space="preserve">751199, 3332171</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -410,16 +410,16 @@
         </is>
       </c>
       <c r="H7">
-        <v>4220</v>
+        <v>460</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041825</t>
+          <t xml:space="preserve">311138078</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-26</t>
+          <t xml:space="preserve">2025-10-02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -451,17 +451,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Skovvej 16</t>
+          <t xml:space="preserve">Jyllandsgade 30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9574</t>
+          <t xml:space="preserve">9520</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">751199, 3332171</t>
+          <t xml:space="preserve">3336242</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,26 +470,26 @@
         </is>
       </c>
       <c r="H8">
-        <v>460</v>
+        <v>254</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">311138078</t>
+          <t xml:space="preserve">311244393</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-02</t>
+          <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jyllandsgade 30</t>
+          <t xml:space="preserve">Strandvejen 15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520</t>
+          <t xml:space="preserve">9610</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3336242</t>
+          <t xml:space="preserve">9402109</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="H9">
-        <v>254</v>
+        <v>2771</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244393</t>
+          <t xml:space="preserve">311603283</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-01</t>
+          <t xml:space="preserve">2032-05-25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -571,35 +571,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 15</t>
+          <t xml:space="preserve">Skovvej 4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9610</t>
+          <t xml:space="preserve">9575</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9402109</t>
+          <t xml:space="preserve">9614946</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H10">
-        <v>2771</v>
+        <v>349</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">311603283</t>
+          <t xml:space="preserve">311632692</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-25</t>
+          <t xml:space="preserve">2032-10-03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -691,35 +691,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 4</t>
+          <t xml:space="preserve">Hjedsbækvej 289</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9575</t>
+          <t xml:space="preserve">9541</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9614946</t>
+          <t xml:space="preserve">7002043</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H12">
-        <v>349</v>
+        <v>1907</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632692</t>
+          <t xml:space="preserve">311642734</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-03</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -766,11 +766,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H13">
-        <v>1907</v>
+        <v>4027</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H14">
-        <v>4027</v>
+        <v>300</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,35 +931,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjedsbækvej 289</t>
+          <t xml:space="preserve">Skibstedvej 26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">9541</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002043</t>
+          <t xml:space="preserve">3335469</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>400</v>
+        <v>990</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642734</t>
+          <t xml:space="preserve">311651018</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1006,11 +1006,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H17">
-        <v>990</v>
+        <v>516</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,35 +1051,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skibstedvej 26</t>
+          <t xml:space="preserve">Birkehøjvej 8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3335469</t>
+          <t xml:space="preserve">3303955</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H18">
-        <v>516</v>
+        <v>3940</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651018</t>
+          <t xml:space="preserve">311651818</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mastrupvej 75</t>
+          <t xml:space="preserve">Hjedsbækvej 287</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9541</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292864</t>
+          <t xml:space="preserve">7002043</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1130,11 +1130,11 @@
         </is>
       </c>
       <c r="H19">
-        <v>7550</v>
+        <v>784</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651797</t>
+          <t xml:space="preserve">311651796</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1171,30 +1171,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mastrupvej 75A</t>
+          <t xml:space="preserve">Løgstørvej 165</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9610</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292864</t>
+          <t xml:space="preserve">3378205</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H20">
-        <v>420</v>
+        <v>486</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651798</t>
+          <t xml:space="preserve">311651820</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mastrupvej 75B</t>
+          <t xml:space="preserve">Mastrupvej 75</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1246,15 +1246,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>903</v>
+        <v>7550</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651799</t>
+          <t xml:space="preserve">311651797</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkehøjvej 8</t>
+          <t xml:space="preserve">Mastrupvej 75A</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,20 +1301,20 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3303955</t>
+          <t xml:space="preserve">3292864</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>3940</v>
+        <v>420</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651818</t>
+          <t xml:space="preserve">311651798</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1351,30 +1351,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rebild Skovhusevej 2</t>
+          <t xml:space="preserve">Mastrupvej 75B</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3335702</t>
+          <t xml:space="preserve">3292864</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H23">
-        <v>1421</v>
+        <v>903</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651794</t>
+          <t xml:space="preserve">311651799</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverriggårdsvej 4</t>
+          <t xml:space="preserve">Rebild Skovhusevej 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3336927</t>
+          <t xml:space="preserve">3335702</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1430,11 +1430,11 @@
         </is>
       </c>
       <c r="H24">
-        <v>970</v>
+        <v>1421</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651823</t>
+          <t xml:space="preserve">311651794</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverriggårdsvej 4</t>
+          <t xml:space="preserve">Sverriggårdsvej 2A</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1486,15 +1486,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H25">
-        <v>254</v>
+        <v>457</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651823</t>
+          <t xml:space="preserve">311651821</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1546,15 +1546,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>1186</v>
+        <v>970</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651823</t>
+          <t xml:space="preserve">311651821</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverriggårdsvej 4A</t>
+          <t xml:space="preserve">Sverriggårdsvej 4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1606,15 +1606,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H27">
-        <v>736</v>
+        <v>254</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651822</t>
+          <t xml:space="preserve">311651823</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverriggårdsvej 2A</t>
+          <t xml:space="preserve">Sverriggårdsvej 4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1666,15 +1666,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>457</v>
+        <v>1186</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651823</t>
+          <t xml:space="preserve">311651821</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1711,30 +1711,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løgstørvej 165</t>
+          <t xml:space="preserve">Sverriggårdsvej 4A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9610</t>
+          <t xml:space="preserve">9520</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378205</t>
+          <t xml:space="preserve">3336927</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H29">
-        <v>486</v>
+        <v>736</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651820</t>
+          <t xml:space="preserve">311651822</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjedsbækvej 287</t>
+          <t xml:space="preserve">Løgstørvej 161</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9541</t>
+          <t xml:space="preserve">9610</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002043</t>
+          <t xml:space="preserve">3378205</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>784</v>
+        <v>622</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651796</t>
+          <t xml:space="preserve">311664900</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-29</t>
+          <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1846,11 +1846,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H31">
-        <v>622</v>
+        <v>800</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1906,11 +1906,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H32">
-        <v>800</v>
+        <v>696</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1966,11 +1966,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H33">
-        <v>696</v>
+        <v>1345</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2026,11 +2026,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H34">
-        <v>1345</v>
+        <v>3110</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2086,11 +2086,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H35">
-        <v>3110</v>
+        <v>1127</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,35 +2131,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løgstørvej 161</t>
+          <t xml:space="preserve">Skørpingvej 7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9610</t>
+          <t xml:space="preserve">9575</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378205</t>
+          <t xml:space="preserve">3333756</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>1127</v>
+        <v>2003</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664900</t>
+          <t xml:space="preserve">311666554</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-08</t>
+          <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skørpingvej 7</t>
+          <t xml:space="preserve">Degnevænget 25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9575</t>
+          <t xml:space="preserve">9520</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333756</t>
+          <t xml:space="preserve">7823049</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="H37">
-        <v>2003</v>
+        <v>467</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666554</t>
+          <t xml:space="preserve">311670128</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-15</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,30 +2251,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terndrup Center 3</t>
+          <t xml:space="preserve">Himmerlandsvej 61</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">9575</t>
+          <t xml:space="preserve">9520</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3334183</t>
+          <t xml:space="preserve">3336437</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H38">
-        <v>588</v>
+        <v>505</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670124</t>
+          <t xml:space="preserve">311670123</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,30 +2311,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terndrup Center 6</t>
+          <t xml:space="preserve">Himmerlandsvej 63</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9575</t>
+          <t xml:space="preserve">9520</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3334184</t>
+          <t xml:space="preserve">3336437</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H39">
-        <v>417</v>
+        <v>510</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670125</t>
+          <t xml:space="preserve">311670123</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsvej 63</t>
+          <t xml:space="preserve">Himmerlandsvej 65</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,15 +2446,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H41">
-        <v>510</v>
+        <v>1935</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670123</t>
+          <t xml:space="preserve">311670120</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2551,30 +2551,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsvej 65</t>
+          <t xml:space="preserve">Terndrup Center 3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520</t>
+          <t xml:space="preserve">9575</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3336437</t>
+          <t xml:space="preserve">3334183</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>1935</v>
+        <v>588</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670120</t>
+          <t xml:space="preserve">311670124</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2611,30 +2611,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsvej 61</t>
+          <t xml:space="preserve">Terndrup Center 6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520</t>
+          <t xml:space="preserve">9575</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3336437</t>
+          <t xml:space="preserve">3334184</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>505</v>
+        <v>417</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670123</t>
+          <t xml:space="preserve">311670125</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnevænget 25</t>
+          <t xml:space="preserve">Bavnebakken 99</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7823049</t>
+          <t xml:space="preserve">3293217</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="H45">
-        <v>467</v>
+        <v>552</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670128</t>
+          <t xml:space="preserve">311671360</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnebakken 99</t>
+          <t xml:space="preserve">Gammel Skolevej 5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3293217</t>
+          <t xml:space="preserve">3303660</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2810,11 +2810,11 @@
         </is>
       </c>
       <c r="H47">
-        <v>552</v>
+        <v>255</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671360</t>
+          <t xml:space="preserve">311671359</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Skolevej 5</t>
+          <t xml:space="preserve">Grangårdsvej 13A</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,20 +2861,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3303660</t>
+          <t xml:space="preserve">7255541</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H48">
-        <v>255</v>
+        <v>683</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671359</t>
+          <t xml:space="preserve">311671364</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2911,30 +2911,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grangårdsvej 13A</t>
+          <t xml:space="preserve">Himmerlandshave 1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9541</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255541</t>
+          <t xml:space="preserve">8149234</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>683</v>
+        <v>3462</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671364</t>
+          <t xml:space="preserve">311671363</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2971,35 +2971,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandshave 1</t>
+          <t xml:space="preserve">Grangårdsvej 11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9541</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8149234</t>
+          <t xml:space="preserve">7255541</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H50">
-        <v>3462</v>
+        <v>1141</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671363</t>
+          <t xml:space="preserve">311682093</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-03</t>
+          <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mastrupvej 63</t>
+          <t xml:space="preserve">Hobrovej 110</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,20 +3041,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3294980</t>
+          <t xml:space="preserve">7255541</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H51">
-        <v>513</v>
+        <v>3384</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682078</t>
+          <t xml:space="preserve">311682070</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grangårdsvej 11</t>
+          <t xml:space="preserve">Kr. Østergårdsvej 2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,20 +3101,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255541</t>
+          <t xml:space="preserve">9851910</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H52">
-        <v>1141</v>
+        <v>1095</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682093</t>
+          <t xml:space="preserve">311682069</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hobrovej 110</t>
+          <t xml:space="preserve">Mastrupvej 63</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,20 +3161,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255541</t>
+          <t xml:space="preserve">3294980</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>3384</v>
+        <v>513</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682070</t>
+          <t xml:space="preserve">311682078</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr. Østergårdsvej 2</t>
+          <t xml:space="preserve">Aavangen 2C</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9575</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9851910</t>
+          <t xml:space="preserve">3333698</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="H54">
-        <v>1095</v>
+        <v>967</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682069</t>
+          <t xml:space="preserve">311685453</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-22</t>
+          <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 1</t>
+          <t xml:space="preserve">Hermesvej 47</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9574</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3331963</t>
+          <t xml:space="preserve">7566589</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,11 +3290,11 @@
         </is>
       </c>
       <c r="H55">
-        <v>3851</v>
+        <v>774</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685452</t>
+          <t xml:space="preserve">311685454</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3331,30 +3331,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aavangen 2C</t>
+          <t xml:space="preserve">Himmerlandshave 2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9575</t>
+          <t xml:space="preserve">9541</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333698</t>
+          <t xml:space="preserve">8149234</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H56">
-        <v>967</v>
+        <v>1028</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685453</t>
+          <t xml:space="preserve">311685451</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hermesvej 47</t>
+          <t xml:space="preserve">Møllevangen 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9574</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7566589</t>
+          <t xml:space="preserve">3331963</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,11 +3470,11 @@
         </is>
       </c>
       <c r="H58">
-        <v>774</v>
+        <v>3851</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685454</t>
+          <t xml:space="preserve">311685452</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandshave 2</t>
+          <t xml:space="preserve">Sortebakken 7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9541</t>
+          <t xml:space="preserve">9610</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8149234</t>
+          <t xml:space="preserve">3378471</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="H59">
-        <v>1028</v>
+        <v>873</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685451</t>
+          <t xml:space="preserve">311685795</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-05</t>
+          <t xml:space="preserve">2033-06-06</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sortebakken 7</t>
+          <t xml:space="preserve">Mastrupvej 90</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9610</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378471</t>
+          <t xml:space="preserve">3292911</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>873</v>
+        <v>755</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685795</t>
+          <t xml:space="preserve">311691495</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-06</t>
+          <t xml:space="preserve">2033-06-29</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mastrupvej 90</t>
+          <t xml:space="preserve">Rafns Alle 3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292911</t>
+          <t xml:space="preserve">3294080</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3650,11 +3650,11 @@
         </is>
       </c>
       <c r="H61">
-        <v>755</v>
+        <v>635</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691495</t>
+          <t xml:space="preserve">311691496</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rafns Alle 3</t>
+          <t xml:space="preserve">Bavnebakken 105</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3294080</t>
+          <t xml:space="preserve">3293205</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="H62">
-        <v>635</v>
+        <v>9432</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691496</t>
+          <t xml:space="preserve">311692210</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-29</t>
+          <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronhjorten 2</t>
+          <t xml:space="preserve">Grangårdsvej 13C</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,20 +3761,20 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">100017011</t>
+          <t xml:space="preserve">7255541</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H63">
-        <v>1111</v>
+        <v>371</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692201</t>
+          <t xml:space="preserve">311692204</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3811,30 +3811,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rebildvej 25A</t>
+          <t xml:space="preserve">Grønnegade 1A</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520</t>
+          <t xml:space="preserve">9574</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054028</t>
+          <t xml:space="preserve">9425182</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H64">
-        <v>361</v>
+        <v>417</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692197</t>
+          <t xml:space="preserve">311692199</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mastruplundvej 2L</t>
+          <t xml:space="preserve">Jernbanegade 18A</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9610</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292865</t>
+          <t xml:space="preserve">3378421</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,11 +3950,11 @@
         </is>
       </c>
       <c r="H66">
-        <v>4266</v>
+        <v>262</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692220</t>
+          <t xml:space="preserve">311692205</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,30 +3991,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnebakken 105</t>
+          <t xml:space="preserve">Jernbanegade 9</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9610</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3293205</t>
+          <t xml:space="preserve">9577061</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H67">
-        <v>9432</v>
+        <v>1230</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692210</t>
+          <t xml:space="preserve">311692206</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4051,30 +4051,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarksvej 2</t>
+          <t xml:space="preserve">Klepholmvej 5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9610</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378118</t>
+          <t xml:space="preserve">9545107</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H68">
-        <v>1134</v>
+        <v>1225</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692224</t>
+          <t xml:space="preserve">311692203</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 18A</t>
+          <t xml:space="preserve">Kronhjorten 2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9610</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3378421</t>
+          <t xml:space="preserve">100017011</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="H69">
-        <v>262</v>
+        <v>1111</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692205</t>
+          <t xml:space="preserve">311692201</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grangårdsvej 13C</t>
+          <t xml:space="preserve">Mastruplundvej 2L</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,20 +4181,20 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255541</t>
+          <t xml:space="preserve">3292865</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>371</v>
+        <v>4266</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692204</t>
+          <t xml:space="preserve">311692220</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4291,30 +4291,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 1A</t>
+          <t xml:space="preserve">Rebildvej 25A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9574</t>
+          <t xml:space="preserve">9520</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425182</t>
+          <t xml:space="preserve">100054028</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H72">
-        <v>417</v>
+        <v>361</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692199</t>
+          <t xml:space="preserve">311692197</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klepholmvej 5</t>
+          <t xml:space="preserve">Rådyret 2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,20 +4361,20 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9545107</t>
+          <t xml:space="preserve">9545112</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H73">
-        <v>1225</v>
+        <v>889</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692203</t>
+          <t xml:space="preserve">311692202</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4411,30 +4411,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådyret 2</t>
+          <t xml:space="preserve">Vestermarksvej 2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9610</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9545112</t>
+          <t xml:space="preserve">3378118</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>889</v>
+        <v>1134</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692202</t>
+          <t xml:space="preserve">311692224</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4471,35 +4471,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 9</t>
+          <t xml:space="preserve">Gammel Skørpingvej 100</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9610</t>
+          <t xml:space="preserve">9520</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9577061</t>
+          <t xml:space="preserve">100024720</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>1230</v>
+        <v>607</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692206</t>
+          <t xml:space="preserve">311697532</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-03</t>
+          <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,17 +4531,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Skørpingvej 100</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9520</t>
+          <t xml:space="preserve">9574</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024720</t>
+          <t xml:space="preserve">9425182</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,11 +4550,11 @@
         </is>
       </c>
       <c r="H76">
-        <v>607</v>
+        <v>3530</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697532</t>
+          <t xml:space="preserve">311697527</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Skørpingvej 5A</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9574</t>
+          <t xml:space="preserve">9575</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425182</t>
+          <t xml:space="preserve">404028, 404029</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>3530</v>
+        <v>2498</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697527</t>
+          <t xml:space="preserve">311703362</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-01</t>
+          <t xml:space="preserve">2033-08-29</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4771,30 +4771,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terndrup Halvej 3</t>
+          <t xml:space="preserve">Bavnebakken 103</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9575</t>
+          <t xml:space="preserve">9530</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">751202, 9614946</t>
+          <t xml:space="preserve">751225, 3293216</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>3007</v>
+        <v>2150</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311756087</t>
+          <t xml:space="preserve">311756082</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,30 +4831,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnebakken 103</t>
+          <t xml:space="preserve">Hjedsbækvej 291</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530</t>
+          <t xml:space="preserve">9541</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">751225, 3293216</t>
+          <t xml:space="preserve">751227, 3306436</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H81">
-        <v>2150</v>
+        <v>2244</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311756082</t>
+          <t xml:space="preserve">311756076</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,30 +4891,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjedsbækvej 291</t>
+          <t xml:space="preserve">Terndrup Halvej 3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9541</t>
+          <t xml:space="preserve">9575</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">751227, 3306436</t>
+          <t xml:space="preserve">751202, 9614946</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H82">
-        <v>2244</v>
+        <v>3007</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311756076</t>
+          <t xml:space="preserve">311756087</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">

--- a/public/exports/29189463.xlsx
+++ b/public/exports/29189463.xlsx
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651821</t>
+          <t xml:space="preserve">311651823</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651821</t>
+          <t xml:space="preserve">311651823</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651821</t>
+          <t xml:space="preserve">311651823</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697529</t>
+          <t xml:space="preserve">311697530</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">

--- a/public/exports/29189463.xlsx
+++ b/public/exports/29189463.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:M83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -239,15 +254,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-09</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -299,15 +319,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-05</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -359,15 +384,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-26</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -419,15 +449,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rask Boligrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-02</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -479,15 +514,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -539,15 +579,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-25</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-03</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-03</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-29</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-08</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-03</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-22</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-05</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hus Check ApS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-06</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-29</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-29</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-03</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-29</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-01</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-01</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-01</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,21 +5389,26 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-16</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L83"/>
+  <autoFilter ref="A1:M83"/>
 </worksheet>
 </file>
--- a/public/exports/29189463.xlsx
+++ b/public/exports/29189463.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">311632692</t>
+          <t xml:space="preserve">311632691</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651823</t>
+          <t xml:space="preserve">311651821</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651823</t>
+          <t xml:space="preserve">311651821</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651823</t>
+          <t xml:space="preserve">311651821</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697530</t>
+          <t xml:space="preserve">311697529</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
